--- a/数据对比/指挥各赛段数据.xlsx
+++ b/数据对比/指挥各赛段数据.xlsx
@@ -220,22 +220,22 @@
         <t>按队伍 T5→T1% 从高到低排名，相同数值并列。</t>
       </text>
     </comment>
-    <comment ref="P11" authorId="0" shapeId="0">
+    <comment ref="P12" authorId="0" shapeId="0">
       <text>
         <t>按该次比赛全部参赛选手的 Dmg dealt / Games 降序排名。</t>
       </text>
     </comment>
-    <comment ref="R11" authorId="0" shapeId="0">
+    <comment ref="R12" authorId="0" shapeId="0">
       <text>
         <t>按队伍 Top 10% 从高到低排名，相同数值并列。</t>
       </text>
     </comment>
-    <comment ref="S11" authorId="0" shapeId="0">
+    <comment ref="S12" authorId="0" shapeId="0">
       <text>
         <t>按队伍 T10→T5% 从高到低排名，相同数值并列。</t>
       </text>
     </comment>
-    <comment ref="T11" authorId="0" shapeId="0">
+    <comment ref="T12" authorId="0" shapeId="0">
       <text>
         <t>按队伍 T5→T1% 从高到低排名，相同数值并列。</t>
       </text>
@@ -245,6 +245,156 @@
 </file>
 
 <file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Codex</author>
+  </authors>
+  <commentList>
+    <comment ref="P2" authorId="0" shapeId="0">
+      <text>
+        <t>按该次比赛全部参赛选手的 Dmg dealt / Games 降序排名。</t>
+      </text>
+    </comment>
+    <comment ref="R2" authorId="0" shapeId="0">
+      <text>
+        <t>按队伍 Top 10% 从高到低排名，相同数值并列。</t>
+      </text>
+    </comment>
+    <comment ref="S2" authorId="0" shapeId="0">
+      <text>
+        <t>按队伍 T10→T5% 从高到低排名，相同数值并列。</t>
+      </text>
+    </comment>
+    <comment ref="T2" authorId="0" shapeId="0">
+      <text>
+        <t>按队伍 T5→T1% 从高到低排名，相同数值并列。</t>
+      </text>
+    </comment>
+    <comment ref="P12" authorId="0" shapeId="0">
+      <text>
+        <t>按该次比赛全部参赛选手的 Dmg dealt / Games 降序排名。</t>
+      </text>
+    </comment>
+    <comment ref="R12" authorId="0" shapeId="0">
+      <text>
+        <t>按队伍 Top 10% 从高到低排名，相同数值并列。</t>
+      </text>
+    </comment>
+    <comment ref="S12" authorId="0" shapeId="0">
+      <text>
+        <t>按队伍 T10→T5% 从高到低排名，相同数值并列。</t>
+      </text>
+    </comment>
+    <comment ref="T12" authorId="0" shapeId="0">
+      <text>
+        <t>按队伍 T5→T1% 从高到低排名，相同数值并列。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Codex</author>
+  </authors>
+  <commentList>
+    <comment ref="P2" authorId="0" shapeId="0">
+      <text>
+        <t>按该次比赛全部参赛选手的 Dmg dealt / Games 降序排名。</t>
+      </text>
+    </comment>
+    <comment ref="R2" authorId="0" shapeId="0">
+      <text>
+        <t>按队伍 Top 10% 从高到低排名，相同数值并列。</t>
+      </text>
+    </comment>
+    <comment ref="S2" authorId="0" shapeId="0">
+      <text>
+        <t>按队伍 T10→T5% 从高到低排名，相同数值并列。</t>
+      </text>
+    </comment>
+    <comment ref="T2" authorId="0" shapeId="0">
+      <text>
+        <t>按队伍 T5→T1% 从高到低排名，相同数值并列。</t>
+      </text>
+    </comment>
+    <comment ref="P12" authorId="0" shapeId="0">
+      <text>
+        <t>按该次比赛全部参赛选手的 Dmg dealt / Games 降序排名。</t>
+      </text>
+    </comment>
+    <comment ref="R12" authorId="0" shapeId="0">
+      <text>
+        <t>按队伍 Top 10% 从高到低排名，相同数值并列。</t>
+      </text>
+    </comment>
+    <comment ref="S12" authorId="0" shapeId="0">
+      <text>
+        <t>按队伍 T10→T5% 从高到低排名，相同数值并列。</t>
+      </text>
+    </comment>
+    <comment ref="T12" authorId="0" shapeId="0">
+      <text>
+        <t>按队伍 T5→T1% 从高到低排名，相同数值并列。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Codex</author>
+  </authors>
+  <commentList>
+    <comment ref="P2" authorId="0" shapeId="0">
+      <text>
+        <t>按该次比赛全部参赛选手的 Dmg dealt / Games 降序排名。</t>
+      </text>
+    </comment>
+    <comment ref="R2" authorId="0" shapeId="0">
+      <text>
+        <t>按队伍 Top 10% 从高到低排名，相同数值并列。</t>
+      </text>
+    </comment>
+    <comment ref="S2" authorId="0" shapeId="0">
+      <text>
+        <t>按队伍 T10→T5% 从高到低排名，相同数值并列。</t>
+      </text>
+    </comment>
+    <comment ref="T2" authorId="0" shapeId="0">
+      <text>
+        <t>按队伍 T5→T1% 从高到低排名，相同数值并列。</t>
+      </text>
+    </comment>
+    <comment ref="P12" authorId="0" shapeId="0">
+      <text>
+        <t>按该次比赛全部参赛选手的 Dmg dealt / Games 降序排名。</t>
+      </text>
+    </comment>
+    <comment ref="R12" authorId="0" shapeId="0">
+      <text>
+        <t>按队伍 Top 10% 从高到低排名，相同数值并列。</t>
+      </text>
+    </comment>
+    <comment ref="S12" authorId="0" shapeId="0">
+      <text>
+        <t>按队伍 T10→T5% 从高到低排名，相同数值并列。</t>
+      </text>
+    </comment>
+    <comment ref="T12" authorId="0" shapeId="0">
+      <text>
+        <t>按队伍 T5→T1% 从高到低排名，相同数值并列。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Codex</author>
@@ -294,156 +444,6 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Codex</author>
-  </authors>
-  <commentList>
-    <comment ref="P2" authorId="0" shapeId="0">
-      <text>
-        <t>按该次比赛全部参赛选手的 Dmg dealt / Games 降序排名。</t>
-      </text>
-    </comment>
-    <comment ref="R2" authorId="0" shapeId="0">
-      <text>
-        <t>按队伍 Top 10% 从高到低排名，相同数值并列。</t>
-      </text>
-    </comment>
-    <comment ref="S2" authorId="0" shapeId="0">
-      <text>
-        <t>按队伍 T10→T5% 从高到低排名，相同数值并列。</t>
-      </text>
-    </comment>
-    <comment ref="T2" authorId="0" shapeId="0">
-      <text>
-        <t>按队伍 T5→T1% 从高到低排名，相同数值并列。</t>
-      </text>
-    </comment>
-    <comment ref="P11" authorId="0" shapeId="0">
-      <text>
-        <t>按该次比赛全部参赛选手的 Dmg dealt / Games 降序排名。</t>
-      </text>
-    </comment>
-    <comment ref="R11" authorId="0" shapeId="0">
-      <text>
-        <t>按队伍 Top 10% 从高到低排名，相同数值并列。</t>
-      </text>
-    </comment>
-    <comment ref="S11" authorId="0" shapeId="0">
-      <text>
-        <t>按队伍 T10→T5% 从高到低排名，相同数值并列。</t>
-      </text>
-    </comment>
-    <comment ref="T11" authorId="0" shapeId="0">
-      <text>
-        <t>按队伍 T5→T1% 从高到低排名，相同数值并列。</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Codex</author>
-  </authors>
-  <commentList>
-    <comment ref="P2" authorId="0" shapeId="0">
-      <text>
-        <t>按该次比赛全部参赛选手的 Dmg dealt / Games 降序排名。</t>
-      </text>
-    </comment>
-    <comment ref="R2" authorId="0" shapeId="0">
-      <text>
-        <t>按队伍 Top 10% 从高到低排名，相同数值并列。</t>
-      </text>
-    </comment>
-    <comment ref="S2" authorId="0" shapeId="0">
-      <text>
-        <t>按队伍 T10→T5% 从高到低排名，相同数值并列。</t>
-      </text>
-    </comment>
-    <comment ref="T2" authorId="0" shapeId="0">
-      <text>
-        <t>按队伍 T5→T1% 从高到低排名，相同数值并列。</t>
-      </text>
-    </comment>
-    <comment ref="P11" authorId="0" shapeId="0">
-      <text>
-        <t>按该次比赛全部参赛选手的 Dmg dealt / Games 降序排名。</t>
-      </text>
-    </comment>
-    <comment ref="R11" authorId="0" shapeId="0">
-      <text>
-        <t>按队伍 Top 10% 从高到低排名，相同数值并列。</t>
-      </text>
-    </comment>
-    <comment ref="S11" authorId="0" shapeId="0">
-      <text>
-        <t>按队伍 T10→T5% 从高到低排名，相同数值并列。</t>
-      </text>
-    </comment>
-    <comment ref="T11" authorId="0" shapeId="0">
-      <text>
-        <t>按队伍 T5→T1% 从高到低排名，相同数值并列。</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Codex</author>
-  </authors>
-  <commentList>
-    <comment ref="P2" authorId="0" shapeId="0">
-      <text>
-        <t>按该次比赛全部参赛选手的 Dmg dealt / Games 降序排名。</t>
-      </text>
-    </comment>
-    <comment ref="R2" authorId="0" shapeId="0">
-      <text>
-        <t>按队伍 Top 10% 从高到低排名，相同数值并列。</t>
-      </text>
-    </comment>
-    <comment ref="S2" authorId="0" shapeId="0">
-      <text>
-        <t>按队伍 T10→T5% 从高到低排名，相同数值并列。</t>
-      </text>
-    </comment>
-    <comment ref="T2" authorId="0" shapeId="0">
-      <text>
-        <t>按队伍 T5→T1% 从高到低排名，相同数值并列。</t>
-      </text>
-    </comment>
-    <comment ref="P10" authorId="0" shapeId="0">
-      <text>
-        <t>按该次比赛全部参赛选手的 Dmg dealt / Games 降序排名。</t>
-      </text>
-    </comment>
-    <comment ref="R10" authorId="0" shapeId="0">
-      <text>
-        <t>按队伍 Top 10% 从高到低排名，相同数值并列。</t>
-      </text>
-    </comment>
-    <comment ref="S10" authorId="0" shapeId="0">
-      <text>
-        <t>按队伍 T10→T5% 从高到低排名，相同数值并列。</t>
-      </text>
-    </comment>
-    <comment ref="T10" authorId="0" shapeId="0">
-      <text>
-        <t>按队伍 T5→T1% 从高到低排名，相同数值并列。</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
@@ -470,22 +470,22 @@
         <t>按队伍 T5→T1% 从高到低排名，相同数值并列。</t>
       </text>
     </comment>
-    <comment ref="P8" authorId="0" shapeId="0">
+    <comment ref="P9" authorId="0" shapeId="0">
       <text>
         <t>按该次比赛全部参赛选手的 Dmg dealt / Games 降序排名。</t>
       </text>
     </comment>
-    <comment ref="R8" authorId="0" shapeId="0">
+    <comment ref="R9" authorId="0" shapeId="0">
       <text>
         <t>按队伍 Top 10% 从高到低排名，相同数值并列。</t>
       </text>
     </comment>
-    <comment ref="S8" authorId="0" shapeId="0">
+    <comment ref="S9" authorId="0" shapeId="0">
       <text>
         <t>按队伍 T10→T5% 从高到低排名，相同数值并列。</t>
       </text>
     </comment>
-    <comment ref="T8" authorId="0" shapeId="0">
+    <comment ref="T9" authorId="0" shapeId="0">
       <text>
         <t>按队伍 T5→T1% 从高到低排名，相同数值并列。</t>
       </text>
@@ -545,8 +545,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Commander1Regular" displayName="Commander1Regular" ref="A2:U8" headerRowCount="1">
-  <autoFilter ref="A2:U8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Commander1Regular" displayName="Commander1Regular" ref="A2:U9" headerRowCount="1">
+  <autoFilter ref="A2:U9"/>
   <tableColumns count="21">
     <tableColumn id="1" name="赛段"/>
     <tableColumn id="2" name="选手"/>
@@ -575,8 +575,8 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Commander6Regular" displayName="Commander6Regular" ref="A2:U5" headerRowCount="1">
-  <autoFilter ref="A2:U5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Commander6Regular" displayName="Commander6Regular" ref="A2:U6" headerRowCount="1">
+  <autoFilter ref="A2:U6"/>
   <tableColumns count="21">
     <tableColumn id="1" name="赛段"/>
     <tableColumn id="2" name="选手"/>
@@ -605,8 +605,8 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Commander6World" displayName="Commander6World" ref="A8:U10" headerRowCount="1">
-  <autoFilter ref="A8:U10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Commander6World" displayName="Commander6World" ref="A9:U11" headerRowCount="1">
+  <autoFilter ref="A9:U11"/>
   <tableColumns count="21">
     <tableColumn id="1" name="赛段"/>
     <tableColumn id="2" name="选手"/>
@@ -695,8 +695,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Commander1World" displayName="Commander1World" ref="A11:U17" headerRowCount="1">
-  <autoFilter ref="A11:U17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Commander1World" displayName="Commander1World" ref="A12:U18" headerRowCount="1">
+  <autoFilter ref="A12:U18"/>
   <tableColumns count="21">
     <tableColumn id="1" name="赛段"/>
     <tableColumn id="2" name="选手"/>
@@ -725,8 +725,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Commander2Regular" displayName="Commander2Regular" ref="A2:U8" headerRowCount="1">
-  <autoFilter ref="A2:U8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Commander2Regular" displayName="Commander2Regular" ref="A2:U9" headerRowCount="1">
+  <autoFilter ref="A2:U9"/>
   <tableColumns count="21">
     <tableColumn id="1" name="赛段"/>
     <tableColumn id="2" name="选手"/>
@@ -755,8 +755,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Commander2World" displayName="Commander2World" ref="A11:U15" headerRowCount="1">
-  <autoFilter ref="A11:U15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Commander2World" displayName="Commander2World" ref="A12:U16" headerRowCount="1">
+  <autoFilter ref="A12:U16"/>
   <tableColumns count="21">
     <tableColumn id="1" name="赛段"/>
     <tableColumn id="2" name="选手"/>
@@ -785,8 +785,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Commander3Regular" displayName="Commander3Regular" ref="A2:U8" headerRowCount="1">
-  <autoFilter ref="A2:U8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Commander3Regular" displayName="Commander3Regular" ref="A2:U9" headerRowCount="1">
+  <autoFilter ref="A2:U9"/>
   <tableColumns count="21">
     <tableColumn id="1" name="赛段"/>
     <tableColumn id="2" name="选手"/>
@@ -815,8 +815,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Commander3World" displayName="Commander3World" ref="A11:U16" headerRowCount="1">
-  <autoFilter ref="A11:U16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Commander3World" displayName="Commander3World" ref="A12:U17" headerRowCount="1">
+  <autoFilter ref="A12:U17"/>
   <tableColumns count="21">
     <tableColumn id="1" name="赛段"/>
     <tableColumn id="2" name="选手"/>
@@ -845,8 +845,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Commander4Regular" displayName="Commander4Regular" ref="A2:U8" headerRowCount="1">
-  <autoFilter ref="A2:U8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Commander4Regular" displayName="Commander4Regular" ref="A2:U9" headerRowCount="1">
+  <autoFilter ref="A2:U9"/>
   <tableColumns count="21">
     <tableColumn id="1" name="赛段"/>
     <tableColumn id="2" name="选手"/>
@@ -875,8 +875,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Commander4World" displayName="Commander4World" ref="A11:U17" headerRowCount="1">
-  <autoFilter ref="A11:U17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Commander4World" displayName="Commander4World" ref="A12:U18" headerRowCount="1">
+  <autoFilter ref="A12:U18"/>
   <tableColumns count="21">
     <tableColumn id="1" name="赛段"/>
     <tableColumn id="2" name="选手"/>
@@ -905,8 +905,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Commander5Regular" displayName="Commander5Regular" ref="A2:U7" headerRowCount="1">
-  <autoFilter ref="A2:U7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Commander5Regular" displayName="Commander5Regular" ref="A2:U8" headerRowCount="1">
+  <autoFilter ref="A2:U8"/>
   <tableColumns count="21">
     <tableColumn id="1" name="赛段"/>
     <tableColumn id="2" name="选手"/>
@@ -1223,7 +1223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U19"/>
+  <dimension ref="A1:U20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1777,194 +1777,194 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="1" t="inlineStr">
+    <row r="9" ht="26.4" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>APAC-S Y6-Split2</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Kassa</t>
+        </is>
+      </c>
+      <c r="C9" s="5">
+        <v>5</v>
+      </c>
+      <c r="D9" s="5">
+        <v>45</v>
+      </c>
+      <c r="E9" s="5">
+        <v>28</v>
+      </c>
+      <c r="F9" s="5">
+        <v>59</v>
+      </c>
+      <c r="G9" s="5">
+        <v>46</v>
+      </c>
+      <c r="H9" s="6">
+        <v>1.891304347826087</v>
+      </c>
+      <c r="I9" s="5">
+        <v>24506</v>
+      </c>
+      <c r="J9" s="5">
+        <v>27633</v>
+      </c>
+      <c r="K9" s="5">
+        <v>-3127</v>
+      </c>
+      <c r="L9" s="6">
+        <v>544.5777777777778</v>
+      </c>
+      <c r="M9" s="7">
+        <v>0.622</v>
+      </c>
+      <c r="N9" s="7">
+        <v>0.536</v>
+      </c>
+      <c r="O9" s="7">
+        <v>0.133</v>
+      </c>
+      <c r="P9" s="5">
+        <v>61</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>98</v>
+      </c>
+      <c r="R9" s="5">
+        <v>6</v>
+      </c>
+      <c r="S9" s="5">
+        <v>13</v>
+      </c>
+      <c r="T9" s="5">
+        <v>19</v>
+      </c>
+      <c r="U9" s="5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>Kassa 世界赛数据</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>赛段</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>选手</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>队伍排名</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Games</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Kills</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Assists</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Deaths</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>KA/D</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Dmg dealt</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Dmg taken</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>Dmg diff</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Dmg dealt/Games</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>Top 10 %</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>T10 -&gt; T5 %</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>T5 -&gt; T1 %</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>场均伤害排名（本次比赛）</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>参赛选手人数</t>
         </is>
       </c>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>Top 10 % 队伍排名</t>
         </is>
       </c>
-      <c r="S11" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>Top 10 -&gt; 5 % 队伍排名</t>
         </is>
       </c>
-      <c r="T11" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
         <is>
           <t>Top 1 % 队伍排名</t>
         </is>
       </c>
-      <c r="U11" s="2" t="inlineStr">
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>参赛队伍数</t>
         </is>
-      </c>
-    </row>
-    <row r="12" ht="26.4" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Y4-S2 Playoffs</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Kassa</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>1.861111111111111</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>18416</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>18431</v>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>-15</v>
-      </c>
-      <c r="L12" s="6" t="n">
-        <v>541.6470588235294</v>
-      </c>
-      <c r="M12" s="7" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="N12" s="7" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="O12" s="7" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v>68</v>
-      </c>
-      <c r="Q12" s="5" t="n">
-        <v>123</v>
-      </c>
-      <c r="R12" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="S12" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="T12" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="U12" s="5" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="13" ht="26.4" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Y4-Championship</t>
+          <t>Y4-S2 Playoffs</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1973,58 +1973,58 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>1.823529411764706</v>
+        <v>1.861111111111111</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>29785</v>
+        <v>18416</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>36524</v>
+        <v>18431</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>-6739</v>
+        <v>-15</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>692.6744186046511</v>
+        <v>541.6470588235294</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>0.651</v>
+        <v>0.647</v>
       </c>
       <c r="N13" s="7" t="n">
-        <v>0.571</v>
+        <v>0.545</v>
       </c>
       <c r="O13" s="7" t="n">
-        <v>0.063</v>
+        <v>0.083</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="R13" s="5" t="n">
         <v>6</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="U13" s="5" t="n">
         <v>40</v>
@@ -2033,7 +2033,7 @@
     <row r="14" ht="26.4" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Y5-S1 Open</t>
+          <t>Y4-Championship</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -2042,67 +2042,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>1.511111111111111</v>
+        <v>1.823529411764706</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>21875</v>
+        <v>29785</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>28142</v>
+        <v>36524</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>-6267</v>
+        <v>-6739</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>607.6388888888889</v>
+        <v>692.6744186046511</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>0.639</v>
+        <v>0.651</v>
       </c>
       <c r="N14" s="7" t="n">
-        <v>0.652</v>
+        <v>0.571</v>
       </c>
       <c r="O14" s="7" t="n">
-        <v>0.133</v>
+        <v>0.063</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>189</v>
+        <v>69</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>448</v>
+        <v>120</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="U14" s="5" t="n">
-        <v>149</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" ht="26.4" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Y5-S1 Playoffs/EWC</t>
+          <t>Y5-S1 Open</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -2111,67 +2111,67 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D15" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.511111111111111</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>21875</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>28142</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>-6267</v>
+      </c>
+      <c r="L15" s="6" t="n">
+        <v>607.6388888888889</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="N15" s="7" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="O15" s="7" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>189</v>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <v>448</v>
+      </c>
+      <c r="R15" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="S15" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="E15" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>3.125</v>
-      </c>
-      <c r="I15" s="5" t="n">
-        <v>13896</v>
-      </c>
-      <c r="J15" s="5" t="n">
-        <v>13984</v>
-      </c>
-      <c r="K15" s="5" t="n">
-        <v>-88</v>
-      </c>
-      <c r="L15" s="6" t="n">
-        <v>731.3684210526316</v>
-      </c>
-      <c r="M15" s="7" t="n">
-        <v>0.737</v>
-      </c>
-      <c r="N15" s="7" t="n">
-        <v>0.643</v>
-      </c>
-      <c r="O15" s="7" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="P15" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q15" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="R15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" s="5" t="n">
-        <v>8</v>
-      </c>
       <c r="T15" s="5" t="n">
-        <v>7</v>
+        <v>78</v>
       </c>
       <c r="U15" s="5" t="n">
-        <v>40</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" ht="26.4" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Y5-Championship</t>
+          <t>Y5-S1 Playoffs/EWC</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -2180,58 +2180,58 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>1.085714285714286</v>
+        <v>3.125</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>15917</v>
+        <v>13896</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>19533</v>
+        <v>13984</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>-3616</v>
+        <v>-88</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>530.5666666666667</v>
+        <v>731.3684210526316</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>0.433</v>
+        <v>0.737</v>
       </c>
       <c r="N16" s="7" t="n">
-        <v>0.385</v>
+        <v>0.643</v>
       </c>
       <c r="O16" s="7" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>120</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="U16" s="5" t="n">
         <v>40</v>
@@ -2240,7 +2240,7 @@
     <row r="17" ht="26.4" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Y6-S1 Playoffs</t>
+          <t>Y5-Championship</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -2249,66 +2249,135 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E17" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F17" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="F17" s="5" t="n">
-        <v>31</v>
-      </c>
       <c r="G17" s="5" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>1.793103448275862</v>
+        <v>1.085714285714286</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>27298</v>
+        <v>15917</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>26752</v>
+        <v>19533</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>546</v>
+        <v>-3616</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>974.9285714285714</v>
+        <v>530.5666666666667</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>0.714</v>
+        <v>0.433</v>
       </c>
       <c r="N17" s="7" t="n">
-        <v>0.25</v>
+        <v>0.385</v>
       </c>
       <c r="O17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>11</v>
+        <v>96</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="U17" s="5" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="18" ht="26.4" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Y6-S1 Playoffs</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Kassa</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1.793103448275862</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>27298</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>26752</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>546</v>
+      </c>
+      <c r="L18" s="6" t="n">
+        <v>974.9285714285714</v>
+      </c>
+      <c r="M18" s="7" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q18" s="5" t="n">
+        <v>121</v>
+      </c>
+      <c r="R18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="T18" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="U18" s="5" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>排名口径：场均伤害在本次比赛全部选手中降序排名；三项 Top 数据在本次比赛全部队伍中降序排名，相同数值并列。</t>
         </is>
@@ -2316,9 +2385,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="A11:U11"/>
     <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A19:U19"/>
+    <mergeCell ref="A20:U20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -2330,980 +2399,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:U17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="13.8" customWidth="1" min="16" max="16"/>
-    <col width="9.6" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="13.8" customWidth="1" min="19" max="19"/>
-    <col width="10.8" customWidth="1" min="20" max="20"/>
-    <col width="9" customWidth="1" min="21" max="21"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CrazyCong 常规赛数据</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="40" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>赛段</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>选手</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>队伍排名</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Games</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Kills</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Assists</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Deaths</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>KA/D</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Dmg dealt</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Dmg taken</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Dmg diff</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Dmg dealt/Games</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>Top 10 %</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>T10 -&gt; T5 %</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>T5 -&gt; T1 %</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>场均伤害排名（本次比赛）</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>参赛选手人数</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>Top 10 % 队伍排名</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>Top 10 -&gt; 5 % 队伍排名</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>Top 1 % 队伍排名</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>参赛队伍数</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="26.4" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>APAC-S Y3-Split2</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>CrazyCong</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="H3" s="6" t="n">
-        <v>1.628571428571429</v>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>14824</v>
-      </c>
-      <c r="J3" s="5" t="n">
-        <v>14466</v>
-      </c>
-      <c r="K3" s="5" t="n">
-        <v>358</v>
-      </c>
-      <c r="L3" s="6" t="n">
-        <v>411.7777777777778</v>
-      </c>
-      <c r="M3" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N3" s="7" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="O3" s="7" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="P3" s="5" t="n">
-        <v>72</v>
-      </c>
-      <c r="Q3" s="5" t="n">
-        <v>102</v>
-      </c>
-      <c r="R3" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="S3" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="T3" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="U3" s="5" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" ht="26.4" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>APAC-S Y4-Split1</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>CrazyCong</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>1.652173913043478</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>24099</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>24712</v>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>-613</v>
-      </c>
-      <c r="L4" s="6" t="n">
-        <v>523.8913043478261</v>
-      </c>
-      <c r="M4" s="7" t="n">
-        <v>0.587</v>
-      </c>
-      <c r="N4" s="7" t="n">
-        <v>0.519</v>
-      </c>
-      <c r="O4" s="7" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q4" s="5" t="n">
-        <v>101</v>
-      </c>
-      <c r="R4" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="S4" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="T4" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="U4" s="5" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" ht="26.4" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>APAC-S Y4-Split2</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>CrazyCong</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>54</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>2.025641025641026</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>25680</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>22882</v>
-      </c>
-      <c r="K5" s="5" t="n">
-        <v>2798</v>
-      </c>
-      <c r="L5" s="6" t="n">
-        <v>597.2093023255813</v>
-      </c>
-      <c r="M5" s="7" t="n">
-        <v>0.721</v>
-      </c>
-      <c r="N5" s="7" t="n">
-        <v>0.581</v>
-      </c>
-      <c r="O5" s="7" t="n">
-        <v>0.278</v>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q5" s="5" t="n">
-        <v>107</v>
-      </c>
-      <c r="R5" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="S5" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="T5" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="U5" s="5" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" ht="26.4" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>APAC-S Y5-Split1</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>CrazyCong</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>82</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>2.333333333333333</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>16801</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>18525</v>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>-1724</v>
-      </c>
-      <c r="L6" s="6" t="n">
-        <v>390.7209302325581</v>
-      </c>
-      <c r="M6" s="7" t="n">
-        <v>0.442</v>
-      </c>
-      <c r="N6" s="7" t="n">
-        <v>0.526</v>
-      </c>
-      <c r="O6" s="7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v>88</v>
-      </c>
-      <c r="Q6" s="5" t="n">
-        <v>101</v>
-      </c>
-      <c r="R6" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="S6" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="T6" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="U6" s="5" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" ht="26.4" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>APAC-S Y5-Split2</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>CrazyCong</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>72</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>2.923076923076923</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>36750</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>31921</v>
-      </c>
-      <c r="K7" s="5" t="n">
-        <v>4829</v>
-      </c>
-      <c r="L7" s="6" t="n">
-        <v>835.2272727272727</v>
-      </c>
-      <c r="M7" s="7" t="n">
-        <v>0.727</v>
-      </c>
-      <c r="N7" s="7" t="n">
-        <v>0.719</v>
-      </c>
-      <c r="O7" s="7" t="n">
-        <v>0.348</v>
-      </c>
-      <c r="P7" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q7" s="5" t="n">
-        <v>106</v>
-      </c>
-      <c r="R7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" s="5" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" ht="26.4" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>APAC-S Y6-Split1</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>CrazyCong</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>2.86046511627907</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>32785</v>
-      </c>
-      <c r="J8" s="5" t="n">
-        <v>24372</v>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>8413</v>
-      </c>
-      <c r="L8" s="6" t="n">
-        <v>745.1136363636364</v>
-      </c>
-      <c r="M8" s="7" t="n">
-        <v>0.659</v>
-      </c>
-      <c r="N8" s="7" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="O8" s="7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="Q8" s="5" t="n">
-        <v>97</v>
-      </c>
-      <c r="R8" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="S8" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="U8" s="5" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>CrazyCong 世界赛数据</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>赛段</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>选手</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>队伍排名</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Games</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Kills</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Assists</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Deaths</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>KA/D</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Dmg dealt</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>Dmg taken</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>Dmg diff</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>Dmg dealt/Games</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>Top 10 %</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>T10 -&gt; T5 %</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>T5 -&gt; T1 %</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>场均伤害排名（本次比赛）</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>参赛选手人数</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>Top 10 % 队伍排名</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>Top 10 -&gt; 5 % 队伍排名</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>Top 1 % 队伍排名</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>参赛队伍数</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="26.4" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Y4-S2 Playoffs</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>CrazyCong</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>1.535714285714286</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>9439</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>10450</v>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>-1011</v>
-      </c>
-      <c r="L12" s="6" t="n">
-        <v>314.6333333333333</v>
-      </c>
-      <c r="M12" s="7" t="n">
-        <v>0.2674</v>
-      </c>
-      <c r="N12" s="7" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="O12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v>119</v>
-      </c>
-      <c r="Q12" s="5" t="n">
-        <v>123</v>
-      </c>
-      <c r="R12" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="S12" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="T12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" s="5" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" ht="26.4" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Y5-S1 Playoffs/EWC</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>CrazyCong</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>1.888888888888889</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>8042</v>
-      </c>
-      <c r="J13" s="5" t="n">
-        <v>11394</v>
-      </c>
-      <c r="K13" s="5" t="n">
-        <v>-3352</v>
-      </c>
-      <c r="L13" s="6" t="n">
-        <v>423.2631578947368</v>
-      </c>
-      <c r="M13" s="7" t="n">
-        <v>0.632</v>
-      </c>
-      <c r="N13" s="7" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="O13" s="7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v>104</v>
-      </c>
-      <c r="Q13" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="R13" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="S13" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="U13" s="5" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" ht="26.4" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Y5-Championship</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>CrazyCong</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>1.064516129032258</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>14668</v>
-      </c>
-      <c r="J14" s="5" t="n">
-        <v>15865</v>
-      </c>
-      <c r="K14" s="5" t="n">
-        <v>-1197</v>
-      </c>
-      <c r="L14" s="6" t="n">
-        <v>488.9333333333333</v>
-      </c>
-      <c r="M14" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N14" s="7" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="O14" s="7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v>103</v>
-      </c>
-      <c r="Q14" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="R14" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="S14" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="T14" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="U14" s="5" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" ht="26.4" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Y6-S1 Playoffs</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>CrazyCong</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>1.657142857142857</v>
-      </c>
-      <c r="I15" s="5" t="n">
-        <v>25270</v>
-      </c>
-      <c r="J15" s="5" t="n">
-        <v>22018</v>
-      </c>
-      <c r="K15" s="5" t="n">
-        <v>3252</v>
-      </c>
-      <c r="L15" s="6" t="n">
-        <v>665</v>
-      </c>
-      <c r="M15" s="7" t="n">
-        <v>0.526</v>
-      </c>
-      <c r="N15" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O15" s="7" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="P15" s="5" t="n">
-        <v>71</v>
-      </c>
-      <c r="Q15" s="5" t="n">
-        <v>121</v>
-      </c>
-      <c r="R15" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="S15" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="T15" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="U15" s="5" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>排名口径：场均伤害在本次比赛全部选手中降序排名；三项 Top 数据在本次比赛全部队伍中降序排名，相同数值并列。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A10:U10"/>
-    <mergeCell ref="A17:U17"/>
-    <mergeCell ref="A1:U1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-  <tableParts count="2">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3338,7 +2433,7 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>3mz 常规赛数据</t>
+          <t>CrazyCong 常规赛数据</t>
         </is>
       </c>
     </row>
@@ -3457,62 +2552,62 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>3mz</t>
+          <t>CrazyCong</t>
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>2.789473684210526</v>
+        <v>1.628571428571429</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>23749</v>
+        <v>14824</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>20933</v>
+        <v>14466</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>2816</v>
+        <v>358</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>565.452380952381</v>
+        <v>411.7777777777778</v>
       </c>
       <c r="M3" s="7" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="N3" s="7" t="n">
-        <v>0.571</v>
+        <v>0.389</v>
       </c>
       <c r="O3" s="7" t="n">
-        <v>0.313</v>
+        <v>0.143</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="Q3" s="5" t="n">
         <v>102</v>
       </c>
       <c r="R3" s="5" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="S3" s="5" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="T3" s="5" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="U3" s="5" t="n">
         <v>31</v>
@@ -3526,62 +2621,62 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>3mz</t>
+          <t>CrazyCong</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>46</v>
       </c>
       <c r="E4" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>1.652173913043478</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>24099</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>24712</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>-613</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>523.8913043478261</v>
+      </c>
+      <c r="M4" s="7" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="N4" s="7" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="O4" s="7" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="P4" s="5" t="n">
         <v>50</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>2.545454545454545</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>28211</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>27318</v>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>893</v>
-      </c>
-      <c r="L4" s="6" t="n">
-        <v>613.2826086956521</v>
-      </c>
-      <c r="M4" s="7" t="n">
-        <v>0.457</v>
-      </c>
-      <c r="N4" s="7" t="n">
-        <v>0.476</v>
-      </c>
-      <c r="O4" s="7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v>32</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>101</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="U4" s="5" t="n">
         <v>34</v>
@@ -3595,62 +2690,62 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>3mz</t>
+          <t>CrazyCong</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>1.975609756097561</v>
+        <v>2.025641025641026</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>23064</v>
+        <v>25680</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>23183</v>
+        <v>22882</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>-119</v>
+        <v>2798</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>562.5365853658536</v>
+        <v>597.2093023255813</v>
       </c>
       <c r="M5" s="7" t="n">
-        <v>0.6</v>
+        <v>0.721</v>
       </c>
       <c r="N5" s="7" t="n">
-        <v>0.542</v>
+        <v>0.581</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>0.154</v>
+        <v>0.278</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>107</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="U5" s="5" t="n">
         <v>37</v>
@@ -3664,62 +2759,62 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>3mz</t>
+          <t>CrazyCong</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>43</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>1.863636363636364</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>23435</v>
+        <v>16801</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>27828</v>
+        <v>18525</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-4393</v>
+        <v>-1724</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>545</v>
+        <v>390.7209302325581</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>0.605</v>
+        <v>0.442</v>
       </c>
       <c r="N6" s="7" t="n">
-        <v>0.538</v>
+        <v>0.526</v>
       </c>
       <c r="O6" s="7" t="n">
-        <v>0.214</v>
+        <v>0.3</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>101</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U6" s="5" t="n">
         <v>30</v>
@@ -3733,62 +2828,62 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>3mz</t>
+          <t>CrazyCong</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>44</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>1.857142857142857</v>
+        <v>2.923076923076923</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>24161</v>
+        <v>36750</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>29365</v>
+        <v>31921</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-5204</v>
+        <v>4829</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>549.1136363636364</v>
+        <v>835.2272727272727</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>0.614</v>
+        <v>0.727</v>
       </c>
       <c r="N7" s="7" t="n">
-        <v>0.556</v>
+        <v>0.719</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>0.2</v>
+        <v>0.348</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>106</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="U7" s="5" t="n">
         <v>30</v>
@@ -3802,315 +2897,315 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>3mz</t>
+          <t>CrazyCong</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>1.513513513513514</v>
+        <v>2.86046511627907</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>20473</v>
+        <v>32785</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>23721</v>
+        <v>24372</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-3248</v>
+        <v>8413</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>568.6944444444445</v>
+        <v>745.1136363636364</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>0.472</v>
+        <v>0.659</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>0.353</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>97</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="U8" s="5" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>3mz 世界赛数据</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="9" ht="26.4" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>APAC-S Y6-Split2</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>CrazyCong</t>
+        </is>
+      </c>
+      <c r="C9" s="5">
+        <v>2</v>
+      </c>
+      <c r="D9" s="5">
+        <v>45</v>
+      </c>
+      <c r="E9" s="5">
+        <v>52</v>
+      </c>
+      <c r="F9" s="5">
+        <v>81</v>
+      </c>
+      <c r="G9" s="5">
+        <v>49</v>
+      </c>
+      <c r="H9" s="6">
+        <v>2.7142857142857144</v>
+      </c>
+      <c r="I9" s="5">
+        <v>29104</v>
+      </c>
+      <c r="J9" s="5">
+        <v>30007</v>
+      </c>
+      <c r="K9" s="5">
+        <v>-903</v>
+      </c>
+      <c r="L9" s="6">
+        <v>646.7555555555556</v>
+      </c>
+      <c r="M9" s="7">
+        <v>0.756</v>
+      </c>
+      <c r="N9" s="7">
+        <v>0.588</v>
+      </c>
+      <c r="O9" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="P9" s="5">
+        <v>41</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>98</v>
+      </c>
+      <c r="R9" s="5">
+        <v>1</v>
+      </c>
+      <c r="S9" s="5">
+        <v>8</v>
+      </c>
+      <c r="T9" s="5">
+        <v>6</v>
+      </c>
+      <c r="U9" s="5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>CrazyCong 世界赛数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>赛段</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>选手</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>队伍排名</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Games</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Kills</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Assists</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Deaths</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>KA/D</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Dmg dealt</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Dmg taken</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>Dmg diff</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Dmg dealt/Games</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>Top 10 %</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>T10 -&gt; T5 %</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>T5 -&gt; T1 %</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>场均伤害排名（本次比赛）</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>参赛选手人数</t>
         </is>
       </c>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>Top 10 % 队伍排名</t>
         </is>
       </c>
-      <c r="S11" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>Top 10 -&gt; 5 % 队伍排名</t>
         </is>
       </c>
-      <c r="T11" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
         <is>
           <t>Top 1 % 队伍排名</t>
         </is>
       </c>
-      <c r="U11" s="2" t="inlineStr">
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>参赛队伍数</t>
         </is>
-      </c>
-    </row>
-    <row r="12" ht="26.4" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Y3-S2 Playoffs</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>3mz</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>1.966666666666667</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>13694</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>16248</v>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>-2554</v>
-      </c>
-      <c r="L12" s="6" t="n">
-        <v>456.4666666666666</v>
-      </c>
-      <c r="M12" s="7" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="N12" s="7" t="n">
-        <v>0.308</v>
-      </c>
-      <c r="O12" s="7" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v>84</v>
-      </c>
-      <c r="Q12" s="5" t="n">
-        <v>122</v>
-      </c>
-      <c r="R12" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="S12" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="T12" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="U12" s="5" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="13" ht="26.4" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Y3-Championship</t>
+          <t>Y4-S2 Playoffs</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>3mz</t>
+          <t>CrazyCong</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>3.379310344827586</v>
+        <v>1.535714285714286</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>21561</v>
+        <v>9439</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>18200</v>
+        <v>10450</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>3361</v>
+        <v>-1011</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>634.1470588235294</v>
+        <v>314.6333333333333</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>0.618</v>
+        <v>0.2674</v>
       </c>
       <c r="N13" s="7" t="n">
-        <v>0.571</v>
+        <v>0.125</v>
       </c>
       <c r="O13" s="7" t="n">
-        <v>0.417</v>
+        <v>1</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>30</v>
+        <v>119</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U13" s="5" t="n">
         <v>40</v>
@@ -4119,67 +3214,67 @@
     <row r="14" ht="26.4" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Y4-S2 Playoffs</t>
+          <t>Y5-S1 Playoffs/EWC</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>3mz</t>
+          <t>CrazyCong</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>12</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>1.871794871794872</v>
+        <v>1.888888888888889</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>17165</v>
+        <v>8042</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>16406</v>
+        <v>11394</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>759</v>
+        <v>-3352</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>429.125</v>
+        <v>423.2631578947368</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>0.525</v>
+        <v>0.632</v>
       </c>
       <c r="N14" s="7" t="n">
-        <v>0.429</v>
+        <v>0.833</v>
       </c>
       <c r="O14" s="7" t="n">
-        <v>0.111</v>
+        <v>0.1</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="U14" s="5" t="n">
         <v>40</v>
@@ -4188,67 +3283,67 @@
     <row r="15" ht="26.4" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Y4-Championship</t>
+          <t>Y5-Championship</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>3mz</t>
+          <t>CrazyCong</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>1.538461538461539</v>
+        <v>1.064516129032258</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>12306</v>
+        <v>14668</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>17033</v>
+        <v>15865</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>-4727</v>
+        <v>-1197</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>473.3076923076923</v>
+        <v>488.9333333333333</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="N15" s="7" t="n">
-        <v>0.333</v>
+        <v>0.667</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>120</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="U15" s="5" t="n">
         <v>40</v>
@@ -4257,67 +3352,67 @@
     <row r="16" ht="26.4" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Y5-S1 Playoffs/EWC</t>
+          <t>Y6-S1 Playoffs</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>3mz</t>
+          <t>CrazyCong</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="D16" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>1.657142857142857</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>25270</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>22018</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>3252</v>
+      </c>
+      <c r="L16" s="6" t="n">
+        <v>665</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="N16" s="7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O16" s="7" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="P16" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q16" s="5" t="n">
+        <v>121</v>
+      </c>
+      <c r="R16" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="S16" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="T16" s="5" t="n">
         <v>10</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>2714</v>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>3747</v>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>-1033</v>
-      </c>
-      <c r="L16" s="6" t="n">
-        <v>271.4</v>
-      </c>
-      <c r="M16" s="7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N16" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="5" t="n">
-        <v>119</v>
-      </c>
-      <c r="Q16" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="R16" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="S16" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" s="5" t="n">
-        <v>23</v>
       </c>
       <c r="U16" s="5" t="n">
         <v>40</v>
@@ -4333,9 +3428,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="A11:U11"/>
+    <mergeCell ref="A18:U18"/>
     <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A18:U18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -4346,7 +3441,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4381,7 +3476,7 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>xd 常规赛数据</t>
+          <t>3mz 常规赛数据</t>
         </is>
       </c>
     </row>
@@ -4500,62 +3595,62 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>xd</t>
+          <t>3mz</t>
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D3" s="5" t="n">
         <v>42</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="G3" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>2.789473684210526</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>23749</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>20933</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>2816</v>
+      </c>
+      <c r="L3" s="6" t="n">
+        <v>565.452380952381</v>
+      </c>
+      <c r="M3" s="7" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="N3" s="7" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="O3" s="7" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="P3" s="5" t="n">
         <v>42</v>
-      </c>
-      <c r="H3" s="6" t="n">
-        <v>1.904761904761905</v>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>26822</v>
-      </c>
-      <c r="J3" s="5" t="n">
-        <v>24993</v>
-      </c>
-      <c r="K3" s="5" t="n">
-        <v>1829</v>
-      </c>
-      <c r="L3" s="6" t="n">
-        <v>638.6190476190476</v>
-      </c>
-      <c r="M3" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N3" s="7" t="n">
-        <v>0.238</v>
-      </c>
-      <c r="O3" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="5" t="n">
-        <v>26</v>
       </c>
       <c r="Q3" s="5" t="n">
         <v>102</v>
       </c>
       <c r="R3" s="5" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="S3" s="5" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="T3" s="5" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="U3" s="5" t="n">
         <v>31</v>
@@ -4569,62 +3664,62 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>xd</t>
+          <t>3mz</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>46</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>2.2</v>
+        <v>2.545454545454545</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>29027</v>
+        <v>28211</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>31377</v>
+        <v>27318</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-2350</v>
+        <v>893</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>631.0217391304348</v>
+        <v>613.2826086956521</v>
       </c>
       <c r="M4" s="7" t="n">
-        <v>0.478</v>
+        <v>0.457</v>
       </c>
       <c r="N4" s="7" t="n">
-        <v>0.455</v>
+        <v>0.476</v>
       </c>
       <c r="O4" s="7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>101</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="U4" s="5" t="n">
         <v>34</v>
@@ -4638,62 +3733,62 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>xd</t>
+          <t>3mz</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D5" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="F5" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="E5" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>71</v>
-      </c>
       <c r="G5" s="5" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>2.977272727272727</v>
+        <v>1.975609756097561</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>29149</v>
+        <v>23064</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>23032</v>
+        <v>23183</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>6117</v>
+        <v>-119</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>677.8837209302326</v>
+        <v>562.5365853658536</v>
       </c>
       <c r="M5" s="7" t="n">
-        <v>0.465</v>
+        <v>0.6</v>
       </c>
       <c r="N5" s="7" t="n">
-        <v>0.5</v>
+        <v>0.542</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>0.3</v>
+        <v>0.154</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>107</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="U5" s="5" t="n">
         <v>37</v>
@@ -4707,62 +3802,62 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>xd</t>
+          <t>3mz</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>43</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>2.767441860465116</v>
+        <v>1.863636363636364</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>29212</v>
+        <v>23435</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>28531</v>
+        <v>27828</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>681</v>
+        <v>-4393</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>679.3488372093024</v>
+        <v>545</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>0.698</v>
+        <v>0.605</v>
       </c>
       <c r="N6" s="7" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.538</v>
       </c>
       <c r="O6" s="7" t="n">
-        <v>0.235</v>
+        <v>0.214</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>101</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U6" s="5" t="n">
         <v>30</v>
@@ -4776,62 +3871,62 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>xd</t>
+          <t>3mz</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>44</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>2.4</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>26072</v>
+        <v>24161</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>25520</v>
+        <v>29365</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>552</v>
+        <v>-5204</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>592.5454545454545</v>
+        <v>549.1136363636364</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>0.386</v>
+        <v>0.614</v>
       </c>
       <c r="N7" s="7" t="n">
-        <v>0.353</v>
+        <v>0.556</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>0.667</v>
+        <v>0.2</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>106</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="U7" s="5" t="n">
         <v>30</v>
@@ -4845,315 +3940,315 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>xd</t>
+          <t>3mz</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>2.431818181818182</v>
+        <v>1.513513513513514</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>28624</v>
+        <v>20473</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>26622</v>
+        <v>23721</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>2002</v>
+        <v>-3248</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>650.5454545454545</v>
+        <v>568.6944444444445</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>0.614</v>
+        <v>0.472</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>0.593</v>
+        <v>0.353</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>97</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="U8" s="5" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>xd 世界赛数据</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="9" ht="26.4" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>APAC-S Y6-Split2</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>3mz</t>
+        </is>
+      </c>
+      <c r="C9" s="5">
+        <v>21</v>
+      </c>
+      <c r="D9" s="5">
+        <v>24</v>
+      </c>
+      <c r="E9" s="5">
+        <v>24</v>
+      </c>
+      <c r="F9" s="5">
+        <v>30</v>
+      </c>
+      <c r="G9" s="5">
+        <v>23</v>
+      </c>
+      <c r="H9" s="6">
+        <v>2.347826086956522</v>
+      </c>
+      <c r="I9" s="5">
+        <v>10891</v>
+      </c>
+      <c r="J9" s="5">
+        <v>13747</v>
+      </c>
+      <c r="K9" s="5">
+        <v>-2856</v>
+      </c>
+      <c r="L9" s="6">
+        <v>453.7916666666667</v>
+      </c>
+      <c r="M9" s="7">
+        <v>0.361</v>
+      </c>
+      <c r="N9" s="7">
+        <v>0.538</v>
+      </c>
+      <c r="O9" s="7">
+        <v>0.143</v>
+      </c>
+      <c r="P9" s="5">
+        <v>81</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>98</v>
+      </c>
+      <c r="R9" s="5">
+        <v>26</v>
+      </c>
+      <c r="S9" s="5">
+        <v>12</v>
+      </c>
+      <c r="T9" s="5">
+        <v>18</v>
+      </c>
+      <c r="U9" s="5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>3mz 世界赛数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>赛段</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>选手</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>队伍排名</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Games</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Kills</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Assists</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Deaths</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>KA/D</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Dmg dealt</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Dmg taken</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>Dmg diff</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Dmg dealt/Games</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>Top 10 %</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>T10 -&gt; T5 %</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>T5 -&gt; T1 %</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>场均伤害排名（本次比赛）</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>参赛选手人数</t>
         </is>
       </c>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>Top 10 % 队伍排名</t>
         </is>
       </c>
-      <c r="S11" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>Top 10 -&gt; 5 % 队伍排名</t>
         </is>
       </c>
-      <c r="T11" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
         <is>
           <t>Top 1 % 队伍排名</t>
         </is>
       </c>
-      <c r="U11" s="2" t="inlineStr">
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>参赛队伍数</t>
         </is>
-      </c>
-    </row>
-    <row r="12" ht="26.4" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Y4-S2 Playoffs</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>xd</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>7397</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>10028</v>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>-2631</v>
-      </c>
-      <c r="L12" s="6" t="n">
-        <v>308.2083333333333</v>
-      </c>
-      <c r="M12" s="7" t="n">
-        <v>0.208</v>
-      </c>
-      <c r="N12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v>119</v>
-      </c>
-      <c r="Q12" s="5" t="n">
-        <v>123</v>
-      </c>
-      <c r="R12" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="S12" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="T12" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="U12" s="5" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="13" ht="26.4" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Y4-Championship</t>
+          <t>Y3-S2 Playoffs</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>xd</t>
+          <t>3mz</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="G13" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1.966666666666667</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>13694</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>16248</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>-2554</v>
+      </c>
+      <c r="L13" s="6" t="n">
+        <v>456.4666666666666</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="O13" s="7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>122</v>
+      </c>
+      <c r="R13" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="H13" s="6" t="n">
-        <v>1.551724137931034</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>16682</v>
-      </c>
-      <c r="J13" s="5" t="n">
-        <v>20834</v>
-      </c>
-      <c r="K13" s="5" t="n">
-        <v>-4152</v>
-      </c>
-      <c r="L13" s="6" t="n">
-        <v>641.6153846153846</v>
-      </c>
-      <c r="M13" s="7" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="N13" s="7" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="O13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v>82</v>
-      </c>
-      <c r="Q13" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="R13" s="5" t="n">
-        <v>22</v>
-      </c>
       <c r="S13" s="5" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="U13" s="5" t="n">
         <v>40</v>
@@ -5162,136 +4257,136 @@
     <row r="14" ht="26.4" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Y5-S1 Open</t>
+          <t>Y3-Championship</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>xd</t>
+          <t>3mz</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>29</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>2.96551724137931</v>
+        <v>3.379310344827586</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>15090</v>
+        <v>21561</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>13600</v>
+        <v>18200</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>1490</v>
+        <v>3361</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>503</v>
+        <v>634.1470588235294</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.618</v>
       </c>
       <c r="N14" s="7" t="n">
-        <v>0.529</v>
+        <v>0.571</v>
       </c>
       <c r="O14" s="7" t="n">
-        <v>0.333</v>
+        <v>0.417</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>286</v>
+        <v>30</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>448</v>
+        <v>121</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="U14" s="5" t="n">
-        <v>149</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" ht="26.4" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Y5-S1 Playoffs/EWC</t>
+          <t>Y4-S2 Playoffs</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>xd</t>
+          <t>3mz</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>1.391304347826087</v>
+        <v>1.871794871794872</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>12276</v>
+        <v>17165</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>13224</v>
+        <v>16406</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>-948</v>
+        <v>759</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>613.8</v>
+        <v>429.125</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>0.45</v>
+        <v>0.525</v>
       </c>
       <c r="N15" s="7" t="n">
-        <v>0.333</v>
+        <v>0.429</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="U15" s="5" t="n">
         <v>40</v>
@@ -5300,67 +4395,67 @@
     <row r="16" ht="26.4" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Y5-Championship</t>
+          <t>Y4-Championship</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>xd</t>
+          <t>3mz</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.5833333333333334</v>
+        <v>1.538461538461539</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>12794</v>
+        <v>12306</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>17451</v>
+        <v>17033</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>-4657</v>
+        <v>-4727</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>533.0833333333334</v>
+        <v>473.3076923076923</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>0.25</v>
+        <v>0.462</v>
       </c>
       <c r="N16" s="7" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="O16" s="7" t="n">
         <v>0</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>120</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="U16" s="5" t="n">
         <v>40</v>
@@ -5369,67 +4464,67 @@
     <row r="17" ht="26.4" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Y6-S1 Playoffs</t>
+          <t>Y5-S1 Playoffs/EWC</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>xd</t>
+          <t>3mz</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>1.233333333333333</v>
+        <v>1.1</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>16447</v>
+        <v>2714</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>20503</v>
+        <v>3747</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>-4056</v>
+        <v>-1033</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>587.3928571428571</v>
+        <v>271.4</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="N17" s="7" t="n">
-        <v>0.286</v>
+        <v>1</v>
       </c>
       <c r="O17" s="7" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="U17" s="5" t="n">
         <v>40</v>
@@ -5445,7 +4540,7 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A10:U10"/>
+    <mergeCell ref="A11:U11"/>
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="A19:U19"/>
   </mergeCells>
@@ -5458,13 +4553,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:U20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -5493,7 +4588,7 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bieyun 常规赛数据</t>
+          <t>xd 常规赛数据</t>
         </is>
       </c>
     </row>
@@ -5607,274 +4702,274 @@
     <row r="3" ht="26.4" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>APAC-S Y4-Split1</t>
+          <t>APAC-S Y3-Split2</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Bieyun</t>
+          <t>xd</t>
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E3" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>1.904761904761905</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>26822</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>24993</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>1829</v>
+      </c>
+      <c r="L3" s="6" t="n">
+        <v>638.6190476190476</v>
+      </c>
+      <c r="M3" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N3" s="7" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="O3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="F3" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="H3" s="6" t="n">
-        <v>1.577777777777778</v>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>21915</v>
-      </c>
-      <c r="J3" s="5" t="n">
-        <v>23180</v>
-      </c>
-      <c r="K3" s="5" t="n">
-        <v>-1265</v>
-      </c>
-      <c r="L3" s="6" t="n">
-        <v>476.4130434782609</v>
-      </c>
-      <c r="M3" s="7" t="n">
-        <v>0.457</v>
-      </c>
-      <c r="N3" s="7" t="n">
-        <v>0.524</v>
-      </c>
-      <c r="O3" s="7" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="P3" s="5" t="n">
-        <v>64</v>
-      </c>
       <c r="Q3" s="5" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="R3" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="S3" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="T3" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="S3" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="T3" s="5" t="n">
-        <v>23</v>
-      </c>
       <c r="U3" s="5" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" ht="26.4" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>APAC-S Y4-Split2</t>
+          <t>APAC-S Y4-Split1</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Bieyun</t>
+          <t>xd</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>1.32</v>
+        <v>2.2</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>10913</v>
+        <v>29027</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>12933</v>
+        <v>31377</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-2020</v>
+        <v>-2350</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>454.7083333333333</v>
+        <v>631.0217391304348</v>
       </c>
       <c r="M4" s="7" t="n">
-        <v>0.552</v>
+        <v>0.478</v>
       </c>
       <c r="N4" s="7" t="n">
-        <v>0.5</v>
+        <v>0.455</v>
       </c>
       <c r="O4" s="7" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="U4" s="5" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" ht="26.4" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>APAC-S Y5-Split1</t>
+          <t>APAC-S Y4-Split2</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Bieyun</t>
+          <t>xd</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>43</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>1.6</v>
+        <v>2.977272727272727</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>20604</v>
+        <v>29149</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>25152</v>
+        <v>23032</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>-4548</v>
+        <v>6117</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>479.1627906976744</v>
+        <v>677.8837209302326</v>
       </c>
       <c r="M5" s="7" t="n">
-        <v>0.628</v>
+        <v>0.465</v>
       </c>
       <c r="N5" s="7" t="n">
-        <v>0.407</v>
+        <v>0.5</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>0.091</v>
+        <v>0.3</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="R5" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="S5" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="T5" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="S5" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="T5" s="5" t="n">
-        <v>22</v>
-      </c>
       <c r="U5" s="5" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" ht="26.4" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>APAC-S Y5-Split2</t>
+          <t>APAC-S Y5-Split1</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Bieyun</t>
+          <t>xd</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>1.5</v>
+        <v>2.767441860465116</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>24499</v>
+        <v>29212</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>29663</v>
+        <v>28531</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-5164</v>
+        <v>681</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>556.7954545454545</v>
+        <v>679.3488372093024</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>0.477</v>
+        <v>0.698</v>
       </c>
       <c r="N6" s="7" t="n">
-        <v>0.381</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="O6" s="7" t="n">
-        <v>0.375</v>
+        <v>0.235</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="U6" s="5" t="n">
         <v>30</v>
@@ -5883,190 +4978,742 @@
     <row r="7" ht="26.4" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>APAC-S Y6-Split1</t>
+          <t>APAC-S Y5-Split2</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Bieyun</t>
+          <t>xd</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>44</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>1.782608695652174</v>
+        <v>2.4</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>25908</v>
+        <v>26072</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>34120</v>
+        <v>25520</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-8212</v>
+        <v>552</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>588.8181818181819</v>
+        <v>592.5454545454545</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>0.636</v>
+        <v>0.386</v>
       </c>
       <c r="N7" s="7" t="n">
-        <v>0.321</v>
+        <v>0.353</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>0.222</v>
+        <v>0.667</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="U7" s="5" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Bieyun 世界赛数据</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="8" ht="26.4" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>APAC-S Y6-Split1</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>xd</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>2.431818181818182</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>28624</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>26622</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>2002</v>
+      </c>
+      <c r="L8" s="6" t="n">
+        <v>650.5454545454545</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="O8" s="7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P8" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q8" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="R8" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="S8" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="U8" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" ht="26.4" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>APAC-S Y6-Split2</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>xd</t>
+        </is>
+      </c>
+      <c r="C9" s="5">
+        <v>8</v>
+      </c>
+      <c r="D9" s="5">
+        <v>45</v>
+      </c>
+      <c r="E9" s="5">
+        <v>51</v>
+      </c>
+      <c r="F9" s="5">
+        <v>77</v>
+      </c>
+      <c r="G9" s="5">
+        <v>42</v>
+      </c>
+      <c r="H9" s="6">
+        <v>3.0476190476190474</v>
+      </c>
+      <c r="I9" s="5">
+        <v>26335</v>
+      </c>
+      <c r="J9" s="5">
+        <v>26243</v>
+      </c>
+      <c r="K9" s="5">
+        <v>92</v>
+      </c>
+      <c r="L9" s="6">
+        <v>585.2222222222222</v>
+      </c>
+      <c r="M9" s="7">
+        <v>0.467</v>
+      </c>
+      <c r="N9" s="7">
+        <v>0.571</v>
+      </c>
+      <c r="O9" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="P9" s="5">
+        <v>50</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>98</v>
+      </c>
+      <c r="R9" s="5">
+        <v>18</v>
+      </c>
+      <c r="S9" s="5">
+        <v>10</v>
+      </c>
+      <c r="T9" s="5">
+        <v>1</v>
+      </c>
+      <c r="U9" s="5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>xd 世界赛数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>赛段</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>选手</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>队伍排名</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Games</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Kills</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Assists</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Deaths</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>KA/D</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Dmg dealt</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Dmg taken</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>Dmg diff</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Dmg dealt/Games</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>Top 10 %</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>T10 -&gt; T5 %</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>T5 -&gt; T1 %</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>场均伤害排名（本次比赛）</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>参赛选手人数</t>
         </is>
       </c>
-      <c r="R10" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>Top 10 % 队伍排名</t>
         </is>
       </c>
-      <c r="S10" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>Top 10 -&gt; 5 % 队伍排名</t>
         </is>
       </c>
-      <c r="T10" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
         <is>
           <t>Top 1 % 队伍排名</t>
         </is>
       </c>
-      <c r="U10" s="2" t="inlineStr">
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>参赛队伍数</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="13" ht="26.4" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Y4-S2 Playoffs</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>xd</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>7397</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>10028</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>-2631</v>
+      </c>
+      <c r="L13" s="6" t="n">
+        <v>308.2083333333333</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>123</v>
+      </c>
+      <c r="R13" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="S13" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="T13" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="U13" s="5" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" ht="26.4" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Y4-Championship</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>xd</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>1.551724137931034</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>16682</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>20834</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>-4152</v>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>641.6153846153846</v>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="N14" s="7" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="O14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q14" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="R14" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="S14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="U14" s="5" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" ht="26.4" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Y5-S1 Open</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>xd</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>2.96551724137931</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>15090</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>13600</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>1490</v>
+      </c>
+      <c r="L15" s="6" t="n">
+        <v>503</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="N15" s="7" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="O15" s="7" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>286</v>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <v>448</v>
+      </c>
+      <c r="R15" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="S15" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="T15" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="U15" s="5" t="n">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="16" ht="26.4" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Y5-S1 Playoffs/EWC</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>xd</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>1.391304347826087</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>12276</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>13224</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>-948</v>
+      </c>
+      <c r="L16" s="6" t="n">
+        <v>613.8</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N16" s="7" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="O16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q16" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="R16" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="S16" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="T16" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="U16" s="5" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" ht="26.4" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Y5-Championship</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>xd</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>12794</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>17451</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>-4657</v>
+      </c>
+      <c r="L17" s="6" t="n">
+        <v>533.0833333333334</v>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N17" s="7" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="O17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q17" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="R17" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="S17" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="U17" s="5" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" ht="26.4" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Y6-S1 Playoffs</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>xd</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1.233333333333333</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>16447</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>20503</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>-4056</v>
+      </c>
+      <c r="L18" s="6" t="n">
+        <v>587.3928571428571</v>
+      </c>
+      <c r="M18" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="O18" s="7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P18" s="5" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q18" s="5" t="n">
+        <v>121</v>
+      </c>
+      <c r="R18" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="S18" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="T18" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="U18" s="5" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>排名口径：场均伤害在本次比赛全部选手中降序排名；三项 Top 数据在本次比赛全部队伍中降序排名，相同数值并列。</t>
         </is>
@@ -6074,25 +5721,26 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A11:U11"/>
     <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A12:U12"/>
-    <mergeCell ref="A9:U9"/>
+    <mergeCell ref="A20:U20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-  <tableParts count="1">
+  <tableParts count="2">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -6121,7 +5769,7 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Jacky 常规赛数据</t>
+          <t>Bieyun 常规赛数据</t>
         </is>
       </c>
     </row>
@@ -6235,139 +5883,139 @@
     <row r="3" ht="26.4" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>APAC-S Y3-Split2</t>
+          <t>APAC-S Y4-Split1</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Jacky</t>
+          <t>Bieyun</t>
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>3.205128205128205</v>
+        <v>1.577777777777778</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>30807</v>
+        <v>21915</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>20825</v>
+        <v>23180</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>9982</v>
+        <v>-1265</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>733.5</v>
+        <v>476.4130434782609</v>
       </c>
       <c r="M3" s="7" t="n">
-        <v>0.643</v>
+        <v>0.457</v>
       </c>
       <c r="N3" s="7" t="n">
-        <v>0.481</v>
+        <v>0.524</v>
       </c>
       <c r="O3" s="7" t="n">
-        <v>0.231</v>
+        <v>0.091</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="Q3" s="5" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R3" s="5" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="S3" s="5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T3" s="5" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="U3" s="5" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" ht="26.4" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>APAC-S Y4-Split1</t>
+          <t>APAC-S Y4-Split2</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Jacky</t>
+          <t>Bieyun</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>2.177777777777778</v>
+        <v>1.32</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>23165</v>
+        <v>10913</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>26004</v>
+        <v>12933</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-2839</v>
+        <v>-2020</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>503.5869565217391</v>
+        <v>454.7083333333333</v>
       </c>
       <c r="M4" s="7" t="n">
-        <v>0.435</v>
+        <v>0.552</v>
       </c>
       <c r="N4" s="7" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="O4" s="7" t="n">
-        <v>0.364</v>
+        <v>0.25</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U4" s="5" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" ht="26.4" customHeight="1">
@@ -6378,323 +6026,392 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Jacky</t>
+          <t>Bieyun</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>1.611111111111111</v>
+        <v>1.6</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>10898</v>
+        <v>20604</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>9545</v>
+        <v>25152</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>1353</v>
+        <v>-4548</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>605.4444444444445</v>
+        <v>479.1627906976744</v>
       </c>
       <c r="M5" s="7" t="n">
-        <v>0.5</v>
+        <v>0.628</v>
       </c>
       <c r="N5" s="7" t="n">
-        <v>0.444</v>
+        <v>0.407</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>101</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="U5" s="5" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Jacky 世界赛数据</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="6" ht="26.4" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>APAC-S Y5-Split2</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Bieyun</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>24499</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>29663</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>-5164</v>
+      </c>
+      <c r="L6" s="6" t="n">
+        <v>556.7954545454545</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="N6" s="7" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="O6" s="7" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" ht="26.4" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>APAC-S Y6-Split1</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Bieyun</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>1.782608695652174</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>25908</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>34120</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>-8212</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>588.8181818181819</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="N7" s="7" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="O7" s="7" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="R7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="S7" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="T7" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="U7" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" ht="26.4" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>APAC-S Y6-Split2</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Bieyun</t>
+        </is>
+      </c>
+      <c r="C8" s="5">
+        <v>14</v>
+      </c>
+      <c r="D8" s="5">
+        <v>45</v>
+      </c>
+      <c r="E8" s="5">
+        <v>32</v>
+      </c>
+      <c r="F8" s="5">
+        <v>28</v>
+      </c>
+      <c r="G8" s="5">
+        <v>48</v>
+      </c>
+      <c r="H8" s="6">
+        <v>1.25</v>
+      </c>
+      <c r="I8" s="5">
+        <v>24493</v>
+      </c>
+      <c r="J8" s="5">
+        <v>29260</v>
+      </c>
+      <c r="K8" s="5">
+        <v>-4767</v>
+      </c>
+      <c r="L8" s="6">
+        <v>544.2888888888889</v>
+      </c>
+      <c r="M8" s="7">
+        <v>0.644</v>
+      </c>
+      <c r="N8" s="7">
+        <v>0.414</v>
+      </c>
+      <c r="O8" s="7">
+        <v>0.083</v>
+      </c>
+      <c r="P8" s="5">
+        <v>62</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>98</v>
+      </c>
+      <c r="R8" s="5">
+        <v>4</v>
+      </c>
+      <c r="S8" s="5">
+        <v>20</v>
+      </c>
+      <c r="T8" s="5">
+        <v>23</v>
+      </c>
+      <c r="U8" s="5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Bieyun 世界赛数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>赛段</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>选手</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>队伍排名</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Games</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Kills</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Assists</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Deaths</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>KA/D</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>Dmg dealt</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Dmg taken</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>Dmg diff</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>Dmg dealt/Games</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>Top 10 %</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>T10 -&gt; T5 %</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>T5 -&gt; T1 %</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>场均伤害排名（本次比赛）</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>参赛选手人数</t>
         </is>
       </c>
-      <c r="R8" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>Top 10 % 队伍排名</t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>Top 10 -&gt; 5 % 队伍排名</t>
         </is>
       </c>
-      <c r="T8" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
         <is>
           <t>Top 1 % 队伍排名</t>
         </is>
       </c>
-      <c r="U8" s="2" t="inlineStr">
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>参赛队伍数</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="26.4" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Y4-S2 Playoffs</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Jacky</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>2.193548387096774</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>12267</v>
-      </c>
-      <c r="J9" s="5" t="n">
-        <v>13046</v>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>-779</v>
-      </c>
-      <c r="L9" s="6" t="n">
-        <v>408.9</v>
-      </c>
-      <c r="M9" s="7" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="N9" s="7" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="O9" s="7" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="P9" s="5" t="n">
-        <v>104</v>
-      </c>
-      <c r="Q9" s="5" t="n">
-        <v>123</v>
-      </c>
-      <c r="R9" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="S9" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="T9" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="U9" s="5" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" ht="26.4" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Y4-Championship</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Jacky</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>1.423076923076923</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>13496</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>15639</v>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>-2143</v>
-      </c>
-      <c r="L10" s="6" t="n">
-        <v>519.0769230769231</v>
-      </c>
-      <c r="M10" s="7" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="N10" s="7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O10" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v>107</v>
-      </c>
-      <c r="Q10" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="R10" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="S10" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="T10" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" s="5" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="12"/>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>排名口径：场均伤害在本次比赛全部选手中降序排名；三项 Top 数据在本次比赛全部队伍中降序排名，相同数值并列。</t>
         </is>
@@ -6703,8 +6420,705 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A12:U12"/>
-    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="A10:U10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="13.8" customWidth="1" min="16" max="16"/>
+    <col width="9.6" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="13.8" customWidth="1" min="19" max="19"/>
+    <col width="10.8" customWidth="1" min="20" max="20"/>
+    <col width="9" customWidth="1" min="21" max="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Jacky 常规赛数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>赛段</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>选手</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>队伍排名</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Kills</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Assists</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Deaths</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>KA/D</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Dmg dealt</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Dmg taken</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Dmg diff</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Dmg dealt/Games</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Top 10 %</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>T10 -&gt; T5 %</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>T5 -&gt; T1 %</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>场均伤害排名（本次比赛）</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>参赛选手人数</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>Top 10 % 队伍排名</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>Top 10 -&gt; 5 % 队伍排名</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>Top 1 % 队伍排名</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>参赛队伍数</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26.4" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>APAC-S Y3-Split2</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Jacky</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>3.205128205128205</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>30807</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>20825</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>9982</v>
+      </c>
+      <c r="L3" s="6" t="n">
+        <v>733.5</v>
+      </c>
+      <c r="M3" s="7" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="N3" s="7" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="O3" s="7" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="P3" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q3" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="R3" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="S3" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="T3" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" ht="26.4" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>APAC-S Y4-Split1</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Jacky</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>2.177777777777778</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>23165</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>26004</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>-2839</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>503.5869565217391</v>
+      </c>
+      <c r="M4" s="7" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="N4" s="7" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O4" s="7" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="P4" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="R4" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="S4" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="T4" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" ht="26.4" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>APAC-S Y5-Split1</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Jacky</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>1.611111111111111</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>10898</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>9545</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>1353</v>
+      </c>
+      <c r="L5" s="6" t="n">
+        <v>605.4444444444445</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N5" s="7" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="O5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="R5" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="S5" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="T5" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="U5" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" ht="26.4" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>APAC-S Y6-Split2</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Jacky</t>
+        </is>
+      </c>
+      <c r="C6" s="5">
+        <v>25</v>
+      </c>
+      <c r="D6" s="5">
+        <v>36</v>
+      </c>
+      <c r="E6" s="5">
+        <v>20</v>
+      </c>
+      <c r="F6" s="5">
+        <v>25</v>
+      </c>
+      <c r="G6" s="5">
+        <v>41</v>
+      </c>
+      <c r="H6" s="6">
+        <v>1.0975609756097562</v>
+      </c>
+      <c r="I6" s="5">
+        <v>14326</v>
+      </c>
+      <c r="J6" s="5">
+        <v>15659</v>
+      </c>
+      <c r="K6" s="5">
+        <v>-1333</v>
+      </c>
+      <c r="L6" s="6">
+        <v>397.94444444444446</v>
+      </c>
+      <c r="M6" s="7">
+        <v>0.333</v>
+      </c>
+      <c r="N6" s="7">
+        <v>0.417</v>
+      </c>
+      <c r="O6" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="P6" s="5">
+        <v>89</v>
+      </c>
+      <c r="Q6" s="5">
+        <v>98</v>
+      </c>
+      <c r="R6" s="5">
+        <v>27</v>
+      </c>
+      <c r="S6" s="5">
+        <v>19</v>
+      </c>
+      <c r="T6" s="5">
+        <v>25</v>
+      </c>
+      <c r="U6" s="5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Jacky 世界赛数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>赛段</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>选手</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>队伍排名</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Kills</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Assists</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Deaths</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>KA/D</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Dmg dealt</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Dmg taken</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Dmg diff</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Dmg dealt/Games</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Top 10 %</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>T10 -&gt; T5 %</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>T5 -&gt; T1 %</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>场均伤害排名（本次比赛）</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>参赛选手人数</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>Top 10 % 队伍排名</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>Top 10 -&gt; 5 % 队伍排名</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>Top 1 % 队伍排名</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>参赛队伍数</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26.4" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Y4-S2 Playoffs</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Jacky</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>2.193548387096774</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>12267</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>13046</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>-779</v>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>408.9</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="O10" s="7" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="P10" s="5" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>123</v>
+      </c>
+      <c r="R10" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="S10" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="T10" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="U10" s="5" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" ht="26.4" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Y4-Championship</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Jacky</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1.423076923076923</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>13496</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>15639</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>-2143</v>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>519.0769230769231</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="N11" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O11" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P11" s="5" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="R11" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="S11" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="T11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" s="5" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>排名口径：场均伤害在本次比赛全部选手中降序排名；三项 Top 数据在本次比赛全部队伍中降序排名，相同数值并列。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A13:U13"/>
+    <mergeCell ref="A8:U8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
